--- a/data/trans_dic/IP19C07-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C07-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por ortodoncia</t>
+          <t>Menores que en su última visita al dentista fue por ortodoncia (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 27,85</t>
+          <t>9,48; 27,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,18; 29,53</t>
+          <t>10,51; 29,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 20,96</t>
+          <t>3,24; 20,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,81; 19,3</t>
+          <t>5,81; 19,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,42; 23,8</t>
+          <t>7,09; 23,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 24,3</t>
+          <t>6,89; 25,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,99; 19,56</t>
+          <t>5,14; 19,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 14,47</t>
+          <t>3,87; 13,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,64; 23,02</t>
+          <t>10,74; 23,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,72; 23,49</t>
+          <t>10,76; 23,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,9; 17,26</t>
+          <t>5,74; 17,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,6; 13,6</t>
+          <t>5,7; 13,54</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,33; 20,59</t>
+          <t>3,84; 20,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,29; 20,57</t>
+          <t>4,86; 20,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,78; 18,17</t>
+          <t>4,76; 17,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,8; 24,67</t>
+          <t>8,58; 24,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 16,77</t>
+          <t>1,7; 16,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 22,0</t>
+          <t>5,69; 20,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,79</t>
+          <t>0,0; 6,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 15,7</t>
+          <t>4,21; 16,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,81; 14,74</t>
+          <t>3,78; 14,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,08; 18,07</t>
+          <t>7,27; 17,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 10,19</t>
+          <t>2,65; 10,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,41; 17,28</t>
+          <t>7,44; 17,36</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 28,95</t>
+          <t>8,41; 29,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,74; 24,07</t>
+          <t>6,53; 23,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 23,15</t>
+          <t>2,82; 22,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 20,47</t>
+          <t>2,37; 19,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 16,09</t>
+          <t>3,63; 15,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 15,45</t>
+          <t>1,6; 14,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,98</t>
+          <t>0,0; 11,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 26,04</t>
+          <t>4,09; 25,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,88; 18,34</t>
+          <t>7,19; 17,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 16,29</t>
+          <t>5,89; 16,78</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 14,52</t>
+          <t>2,61; 13,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,92; 18,44</t>
+          <t>4,14; 18,29</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,19; 15,41</t>
+          <t>5,12; 15,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 12,31</t>
+          <t>2,95; 12,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 10,53</t>
+          <t>2,8; 10,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 10,08</t>
+          <t>2,23; 9,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,75; 20,91</t>
+          <t>9,01; 20,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 9,61</t>
+          <t>1,98; 8,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 10,88</t>
+          <t>2,98; 10,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 10,36</t>
+          <t>1,64; 9,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,43; 16,08</t>
+          <t>8,45; 15,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 8,73</t>
+          <t>3,36; 8,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 9,28</t>
+          <t>3,65; 9,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 8,0</t>
+          <t>2,77; 8,18</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 15,33</t>
+          <t>2,73; 14,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,85</t>
+          <t>0,84; 8,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,68; 17,77</t>
+          <t>5,7; 18,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 13,18</t>
+          <t>1,87; 12,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 12,27</t>
+          <t>2,78; 11,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,29; 18,6</t>
+          <t>5,83; 19,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 11,89</t>
+          <t>2,42; 12,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,12</t>
+          <t>0,61; 7,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,67; 11,42</t>
+          <t>3,65; 11,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,1; 11,66</t>
+          <t>4,21; 11,4</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,73; 12,26</t>
+          <t>4,89; 12,46</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 6,88</t>
+          <t>1,55; 7,0</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,9; 33,45</t>
+          <t>11,65; 33,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,19; 35,58</t>
+          <t>8,34; 36,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,05; 22,67</t>
+          <t>3,0; 21,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,35</t>
+          <t>0,0; 14,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,85; 18,22</t>
+          <t>1,84; 16,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,18; 34,11</t>
+          <t>10,9; 34,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,33; 21,0</t>
+          <t>2,26; 20,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,32</t>
+          <t>0,0; 13,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,15; 22,32</t>
+          <t>9,32; 22,01</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,5; 29,92</t>
+          <t>12,73; 28,93</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,22; 17,03</t>
+          <t>4,24; 16,4</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,0</t>
+          <t>0,99; 10,05</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,95; 15,78</t>
+          <t>9,83; 15,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,48; 12,92</t>
+          <t>7,51; 12,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,16; 11,61</t>
+          <t>6,33; 11,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,61; 10,47</t>
+          <t>5,64; 10,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,61; 12,89</t>
+          <t>7,52; 12,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,01; 13,49</t>
+          <t>7,77; 13,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,16; 8,48</t>
+          <t>4,27; 8,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,03</t>
+          <t>4,01; 8,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,36; 13,48</t>
+          <t>9,51; 13,24</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,41; 12,19</t>
+          <t>8,41; 12,44</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,85; 9,16</t>
+          <t>5,73; 9,11</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,17; 8,12</t>
+          <t>5,22; 8,27</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por ortodoncia (tasa de respuesta: 99,51%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>9587</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9158</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4198</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7995</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>6950</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5742</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5392</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>7166</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>16537</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14900</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>9590</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>15162</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5195; 14938</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5149; 14499</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1392; 8955</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4167; 14111</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3501; 11811</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2818; 10570</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2596; 10030</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3722; 13300</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>11187; 24038</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9673; 21096</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5369; 16260</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>9573; 22725</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4092</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5393</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5568</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9699</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2276</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>6430</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>6012</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>6368</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11823</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>6293</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>15711</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1556; 8150</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2308; 9831</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2654; 9986</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5378; 15423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>629; 6109</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3019; 11039</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3612</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>3015; 11958</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2928; 11192</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>7314; 17737</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2908; 11212</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>9989; 23319</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5770</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5659</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2226</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4563</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2591</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4249</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>10333</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>8250</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4491</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>6476</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2946; 10210</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2723; 9897</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>900; 7023</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>663; 5401</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1935; 8468</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>635; 5892</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3861</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1482; 9372</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>6351; 15316</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4801; 13681</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1731; 8935</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2660; 11743</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5906</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6422</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5534</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4552</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6495</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5441</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>22803</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>10458</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>12917</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>10976</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>5027; 15492</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2694; 11061</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3110; 12159</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2477; 10618</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>8665; 19961</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1939; 8669</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3097; 11407</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2089; 12527</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>16413; 30626</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>6356; 16487</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>7842; 20939</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>6594; 19501</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>4139</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2663</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7264</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3533</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4115</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>8272</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4268</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2605</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>8255</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>10935</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>11533</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1492; 8089</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>691; 6631</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3939; 12646</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1281; 8892</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1944; 8318</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4297; 14357</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1777; 9399</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>624; 7253</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>4546; 14376</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>6565; 17778</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>6982; 17782</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2660; 12012</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>8226</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4903</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2968</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2622</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>7760</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2796</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1870</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>10847</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>12663</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5763</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3240</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>4658; 13530</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2142; 9283</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>979; 7004</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 6347</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>656; 5835</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>4091; 12862</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>727; 6736</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5912</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>7055; 16665</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>8047; 18284</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2749; 10629</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>882; 8943</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>41016</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>33681</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>29692</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>30358</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>34127</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>35347</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>20895</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>27344</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>75143</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>69028</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>50587</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>57703</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>31757; 50950</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>25335; 43357</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>21745; 38934</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>21804; 40437</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>25696; 43056</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>26655; 44904</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>14884; 29415</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>19202; 38740</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>63252; 88019</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>57219; 84650</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>39638; 63036</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>45187; 71541</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C07-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C07-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,48; 27,26</t>
+          <t>9,74; 27,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,51; 29,61</t>
+          <t>10,88; 29,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,24; 20,82</t>
+          <t>3,25; 20,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,81; 19,66</t>
+          <t>5,63; 19,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,09; 23,93</t>
+          <t>8,23; 24,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,89; 25,85</t>
+          <t>6,39; 23,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 19,86</t>
+          <t>5,24; 20,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,87; 13,84</t>
+          <t>3,54; 13,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,74; 23,08</t>
+          <t>10,34; 21,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,76; 23,48</t>
+          <t>10,94; 23,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,74; 17,38</t>
+          <t>5,7; 16,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 13,54</t>
+          <t>5,64; 13,92</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 20,13</t>
+          <t>3,76; 20,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 20,7</t>
+          <t>5,26; 20,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 17,92</t>
+          <t>4,65; 17,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,58; 24,6</t>
+          <t>8,49; 25,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 16,49</t>
+          <t>1,68; 16,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,69; 20,8</t>
+          <t>6,38; 22,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,69</t>
+          <t>0,0; 6,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 16,7</t>
+          <t>3,88; 15,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 14,43</t>
+          <t>4,21; 14,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,27; 17,64</t>
+          <t>7,09; 18,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 10,21</t>
+          <t>2,97; 10,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,44; 17,36</t>
+          <t>7,39; 17,2</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,41; 29,16</t>
+          <t>7,87; 27,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 23,72</t>
+          <t>6,76; 25,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 22,01</t>
+          <t>2,59; 22,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 19,34</t>
+          <t>2,48; 22,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 15,87</t>
+          <t>3,54; 15,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 14,81</t>
+          <t>1,62; 14,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,26</t>
+          <t>0,0; 11,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,09; 25,85</t>
+          <t>3,98; 23,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,19; 17,33</t>
+          <t>6,93; 18,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,89; 16,78</t>
+          <t>5,43; 16,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 13,5</t>
+          <t>2,95; 14,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,14; 18,29</t>
+          <t>4,86; 20,0</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,12; 15,79</t>
+          <t>5,23; 15,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 12,12</t>
+          <t>3,38; 11,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 10,94</t>
+          <t>2,62; 11,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 9,56</t>
+          <t>2,23; 8,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,01; 20,76</t>
+          <t>9,07; 21,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 8,85</t>
+          <t>1,99; 9,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 10,98</t>
+          <t>2,91; 11,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 9,83</t>
+          <t>1,53; 9,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,45; 15,76</t>
+          <t>8,26; 15,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 8,71</t>
+          <t>3,44; 8,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 9,74</t>
+          <t>3,79; 9,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 8,18</t>
+          <t>2,52; 7,69</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 14,8</t>
+          <t>3,59; 15,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,06</t>
+          <t>0,84; 7,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,7; 18,28</t>
+          <t>5,68; 18,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 12,98</t>
+          <t>1,37; 11,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 11,88</t>
+          <t>2,25; 12,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 19,49</t>
+          <t>5,78; 19,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 12,77</t>
+          <t>2,48; 12,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 7,03</t>
+          <t>0,65; 7,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 11,53</t>
+          <t>3,63; 10,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,21; 11,4</t>
+          <t>4,17; 11,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,89; 12,46</t>
+          <t>4,8; 12,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 7,0</t>
+          <t>1,48; 6,76</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,65; 33,83</t>
+          <t>11,35; 32,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,34; 36,14</t>
+          <t>8,04; 35,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,0; 21,48</t>
+          <t>2,07; 21,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,15</t>
+          <t>0,0; 16,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 16,33</t>
+          <t>1,83; 18,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,9; 34,28</t>
+          <t>12,23; 34,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,26; 20,93</t>
+          <t>2,08; 19,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,4</t>
+          <t>0,0; 13,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,32; 22,01</t>
+          <t>8,88; 21,79</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,73; 28,93</t>
+          <t>12,59; 29,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,24; 16,4</t>
+          <t>4,08; 16,45</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 10,05</t>
+          <t>0,98; 9,72</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,83; 15,77</t>
+          <t>9,8; 16,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,51; 12,85</t>
+          <t>7,53; 12,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,33; 11,33</t>
+          <t>6,31; 11,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,64; 10,45</t>
+          <t>5,79; 10,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,52; 12,6</t>
+          <t>7,67; 12,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,77; 13,1</t>
+          <t>7,56; 13,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,27; 8,44</t>
+          <t>4,1; 8,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,01; 8,09</t>
+          <t>4,06; 8,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,51; 13,24</t>
+          <t>9,48; 13,34</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,41; 12,44</t>
+          <t>8,27; 12,03</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,73; 9,11</t>
+          <t>5,78; 9,13</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,22; 8,27</t>
+          <t>5,25; 8,43</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5195; 14938</t>
+          <t>5339; 14966</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5149; 14499</t>
+          <t>5329; 14536</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1392; 8955</t>
+          <t>1397; 8868</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4167; 14111</t>
+          <t>4043; 13656</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3501; 11811</t>
+          <t>4060; 12276</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2818; 10570</t>
+          <t>2611; 9726</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2596; 10030</t>
+          <t>2647; 10280</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3722; 13300</t>
+          <t>3402; 12566</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11187; 24038</t>
+          <t>10773; 22678</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9673; 21096</t>
+          <t>9828; 21297</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5369; 16260</t>
+          <t>5332; 15775</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9573; 22725</t>
+          <t>9462; 23367</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1556; 8150</t>
+          <t>1523; 8277</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2308; 9831</t>
+          <t>2496; 9654</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2654; 9986</t>
+          <t>2590; 9915</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5378; 15423</t>
+          <t>5323; 15891</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>629; 6109</t>
+          <t>624; 6152</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3019; 11039</t>
+          <t>3385; 12035</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3612</t>
+          <t>0; 3654</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3015; 11958</t>
+          <t>2774; 10929</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2928; 11192</t>
+          <t>3261; 11422</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7314; 17737</t>
+          <t>7135; 18412</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2908; 11212</t>
+          <t>3260; 11667</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9989; 23319</t>
+          <t>9925; 23100</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2946; 10210</t>
+          <t>2757; 9709</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2723; 9897</t>
+          <t>2822; 10583</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>900; 7023</t>
+          <t>826; 7297</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>663; 5401</t>
+          <t>694; 6199</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1935; 8468</t>
+          <t>1887; 8512</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>635; 5892</t>
+          <t>643; 5866</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3861</t>
+          <t>0; 3990</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1482; 9372</t>
+          <t>1444; 8592</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6351; 15316</t>
+          <t>6124; 16036</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4801; 13681</t>
+          <t>4430; 13603</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1731; 8935</t>
+          <t>1955; 9761</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2660; 11743</t>
+          <t>3119; 12838</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5027; 15492</t>
+          <t>5137; 15374</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2694; 11061</t>
+          <t>3083; 10810</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3110; 12159</t>
+          <t>2907; 12344</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2477; 10618</t>
+          <t>2475; 9955</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8665; 19961</t>
+          <t>8726; 20548</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1939; 8669</t>
+          <t>1954; 9560</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3097; 11407</t>
+          <t>3024; 11587</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2089; 12527</t>
+          <t>1950; 12675</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16413; 30626</t>
+          <t>16045; 30821</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6356; 16487</t>
+          <t>6517; 16447</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7842; 20939</t>
+          <t>8145; 19545</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6594; 19501</t>
+          <t>6018; 18333</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1492; 8089</t>
+          <t>1965; 8532</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>691; 6631</t>
+          <t>693; 6244</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3939; 12646</t>
+          <t>3931; 12996</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1281; 8892</t>
+          <t>940; 7732</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1944; 8318</t>
+          <t>1578; 8547</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4297; 14357</t>
+          <t>4257; 14192</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1777; 9399</t>
+          <t>1823; 8997</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>624; 7253</t>
+          <t>668; 7900</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4546; 14376</t>
+          <t>4528; 13636</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6565; 17778</t>
+          <t>6505; 17166</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6982; 17782</t>
+          <t>6845; 18319</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2660; 12012</t>
+          <t>2537; 11601</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4658; 13530</t>
+          <t>4538; 13160</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2142; 9283</t>
+          <t>2065; 9176</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>979; 7004</t>
+          <t>674; 6904</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 6347</t>
+          <t>0; 7385</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>656; 5835</t>
+          <t>653; 6504</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4091; 12862</t>
+          <t>4589; 12861</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>727; 6736</t>
+          <t>669; 6238</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 5912</t>
+          <t>0; 5880</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7055; 16665</t>
+          <t>6726; 16498</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8047; 18284</t>
+          <t>7955; 18591</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2749; 10629</t>
+          <t>2644; 10659</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>882; 8943</t>
+          <t>871; 8651</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>31757; 50950</t>
+          <t>31656; 51695</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25335; 43357</t>
+          <t>25405; 43549</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21745; 38934</t>
+          <t>21662; 39563</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21804; 40437</t>
+          <t>22388; 40492</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>25696; 43056</t>
+          <t>26202; 44209</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26655; 44904</t>
+          <t>25916; 45834</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14884; 29415</t>
+          <t>14275; 28837</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>19202; 38740</t>
+          <t>19431; 39582</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>63252; 88019</t>
+          <t>63049; 88661</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>57219; 84650</t>
+          <t>56237; 81815</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>39638; 63036</t>
+          <t>40003; 63213</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>45187; 71541</t>
+          <t>45443; 72984</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C07-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C07-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14,08%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14,04%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7,92%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>17,5%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>18,7%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>9,76%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,14%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,08%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,74; 27,31</t>
+          <t>7,42; 23,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,88; 29,68</t>
+          <t>6,94; 24,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,25; 20,61</t>
+          <t>4,99; 19,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 19,03</t>
+          <t>4,04; 15,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,23; 24,87</t>
+          <t>10,28; 27,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,39; 23,79</t>
+          <t>10,18; 29,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 20,35</t>
+          <t>3,27; 20,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 13,08</t>
+          <t>6,21; 20,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,34; 21,77</t>
+          <t>10,64; 23,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,94; 23,7</t>
+          <t>10,72; 23,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 16,87</t>
+          <t>5,9; 17,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 13,92</t>
+          <t>6,03; 14,63</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12,12%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>10,1%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>11,35%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>9,99%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15,47%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,12%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 20,44</t>
+          <t>1,72; 16,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,26; 20,33</t>
+          <t>5,46; 22,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 17,79</t>
+          <t>0,0; 6,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,49; 25,34</t>
+          <t>3,7; 16,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 16,61</t>
+          <t>4,33; 20,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,38; 22,68</t>
+          <t>5,29; 20,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,76</t>
+          <t>4,78; 18,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 15,27</t>
+          <t>8,47; 23,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 14,73</t>
+          <t>3,81; 14,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,09; 18,31</t>
+          <t>7,08; 18,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 10,63</t>
+          <t>2,71; 10,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,39; 17,2</t>
+          <t>7,22; 17,15</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12,41%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>16,48%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>13,56%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>10,26%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,55%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,87; 27,73</t>
+          <t>3,68; 16,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,76; 25,36</t>
+          <t>1,64; 15,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 22,87</t>
+          <t>0,0; 11,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 22,2</t>
+          <t>4,57; 27,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 15,95</t>
+          <t>7,49; 28,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 14,74</t>
+          <t>6,74; 24,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,63</t>
+          <t>2,83; 23,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 23,69</t>
+          <t>2,29; 20,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,93; 18,14</t>
+          <t>6,88; 18,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,43; 16,69</t>
+          <t>5,2; 16,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 14,74</t>
+          <t>3,1; 14,52</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,86; 20,0</t>
+          <t>5,05; 19,14</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14,15%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,25%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9,38%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6,47%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5,78%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,15%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 15,67</t>
+          <t>8,75; 20,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 11,85</t>
+          <t>1,98; 9,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 11,11</t>
+          <t>2,82; 10,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 8,97</t>
+          <t>1,83; 10,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,07; 21,37</t>
+          <t>5,19; 15,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,76</t>
+          <t>3,41; 12,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 11,16</t>
+          <t>2,98; 10,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 9,95</t>
+          <t>2,63; 10,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,26; 15,86</t>
+          <t>8,43; 16,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 8,69</t>
+          <t>3,26; 8,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 9,09</t>
+          <t>3,5; 9,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 7,69</t>
+          <t>2,82; 8,35</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,88%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11,23%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>7,57%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>3,24%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,23%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,59; 15,61</t>
+          <t>2,08; 12,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,59</t>
+          <t>6,29; 18,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,68; 18,79</t>
+          <t>2,19; 11,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 11,29</t>
+          <t>0,0; 7,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 12,2</t>
+          <t>3,42; 15,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,78; 19,26</t>
+          <t>0,84; 7,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 12,23</t>
+          <t>5,68; 17,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 7,65</t>
+          <t>1,81; 14,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 10,94</t>
+          <t>3,67; 11,42</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,17; 11,01</t>
+          <t>4,1; 11,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 12,83</t>
+          <t>4,73; 12,26</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,76</t>
+          <t>1,61; 7,26</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20,68%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8,69%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>20,56%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>19,08%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>9,1%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20,68%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,69%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,35; 32,9</t>
+          <t>1,85; 18,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,04; 35,72</t>
+          <t>11,18; 34,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,07; 21,18</t>
+          <t>2,33; 21,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,46</t>
+          <t>0,0; 13,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 18,2</t>
+          <t>11,9; 33,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,23; 34,28</t>
+          <t>8,19; 35,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 19,38</t>
+          <t>2,05; 22,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,32</t>
+          <t>0,0; 16,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,88; 21,79</t>
+          <t>9,15; 22,32</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,59; 29,41</t>
+          <t>12,5; 29,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,08; 16,45</t>
+          <t>4,22; 17,03</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,98; 9,72</t>
+          <t>0,98; 10,45</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9,99%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10,31%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6,0%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6,0%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>12,69%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>9,98%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>8,64%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,31%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,8; 16,0</t>
+          <t>7,61; 12,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,53; 12,91</t>
+          <t>8,01; 13,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,31; 11,52</t>
+          <t>4,16; 8,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,79; 10,47</t>
+          <t>4,3; 8,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,67; 12,94</t>
+          <t>9,95; 15,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,56; 13,37</t>
+          <t>7,48; 12,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,1; 8,28</t>
+          <t>6,16; 11,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,06; 8,27</t>
+          <t>5,78; 10,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,48; 13,34</t>
+          <t>9,36; 13,48</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,27; 12,03</t>
+          <t>8,41; 12,19</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,13</t>
+          <t>5,85; 9,16</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,43</t>
+          <t>5,41; 8,5</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,37 +1791,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6950</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5742</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5392</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7171</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>9587</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>9158</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4198</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7995</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>6950</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5742</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5392</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>15597</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5339; 14966</t>
+          <t>3660; 11748</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5329; 14536</t>
+          <t>2836; 9937</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1397; 8868</t>
+          <t>2520; 9879</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4043; 13656</t>
+          <t>3657; 14425</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4060; 12276</t>
+          <t>5631; 15259</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2611; 9726</t>
+          <t>4986; 14464</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2647; 10280</t>
+          <t>1406; 9019</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3402; 12566</t>
+          <t>4443; 14471</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10773; 22678</t>
+          <t>11086; 23975</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9828; 21297</t>
+          <t>9632; 21106</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5332; 15775</t>
+          <t>5516; 16143</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9462; 23367</t>
+          <t>9775; 23715</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2276</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6430</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6048</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4092</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5393</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>5568</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9699</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2276</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6430</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15711</t>
+          <t>15851</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1523; 8277</t>
+          <t>638; 6214</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2496; 9654</t>
+          <t>2899; 11675</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2590; 9915</t>
+          <t>0; 3669</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5323; 15891</t>
+          <t>2607; 11452</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>624; 6152</t>
+          <t>1752; 8337</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3385; 12035</t>
+          <t>2515; 9770</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3654</t>
+          <t>2664; 10128</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2774; 10929</t>
+          <t>5525; 15638</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3261; 11422</t>
+          <t>2953; 11427</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7135; 18412</t>
+          <t>7120; 18172</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3260; 11667</t>
+          <t>2972; 11186</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9925; 23100</t>
+          <t>9790; 23259</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4563</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2591</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4282</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>5770</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>5659</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3272</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2226</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4563</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2591</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1219</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>6551</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2757; 9709</t>
+          <t>1964; 8585</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2822; 10583</t>
+          <t>652; 6149</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>826; 7297</t>
+          <t>0; 4109</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>694; 6199</t>
+          <t>1576; 9466</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1887; 8512</t>
+          <t>2624; 10135</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>643; 5866</t>
+          <t>2811; 10041</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3990</t>
+          <t>902; 7387</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1444; 8592</t>
+          <t>664; 5802</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6124; 16036</t>
+          <t>6084; 16211</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4430; 13603</t>
+          <t>4235; 13279</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1955; 9761</t>
+          <t>2055; 9609</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3119; 12838</t>
+          <t>3204; 12155</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4552</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6495</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5474</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>9202</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5906</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>6422</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5534</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>13601</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4552</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6495</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10976</t>
+          <t>11172</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5137; 15374</t>
+          <t>8414; 20102</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3083; 10810</t>
+          <t>1941; 9419</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2907; 12344</t>
+          <t>2926; 11302</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2475; 9955</t>
+          <t>2236; 12914</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8726; 20548</t>
+          <t>5090; 15128</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1954; 9560</t>
+          <t>3114; 11228</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3024; 11587</t>
+          <t>3307; 11703</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1950; 12675</t>
+          <t>2866; 11620</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16045; 30821</t>
+          <t>16386; 31243</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6517; 16447</t>
+          <t>6162; 16513</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8145; 19545</t>
+          <t>7533; 19952</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6018; 18333</t>
+          <t>6533; 19323</t>
         </is>
       </c>
     </row>
@@ -2628,37 +2628,37 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4115</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8272</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4268</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2497</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>4139</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2663</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>7264</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3533</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4115</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8272</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>4268</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6231</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1965; 8532</t>
+          <t>1460; 8596</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>693; 6244</t>
+          <t>4636; 13702</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3931; 12996</t>
+          <t>1609; 8753</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>940; 7732</t>
+          <t>0; 7111</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1578; 8547</t>
+          <t>1868; 8380</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4257; 14192</t>
+          <t>695; 6455</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1823; 8997</t>
+          <t>3925; 12293</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>668; 7900</t>
+          <t>1249; 9884</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4528; 13636</t>
+          <t>4571; 14238</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6505; 17166</t>
+          <t>6389; 18178</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6845; 18319</t>
+          <t>6757; 17498</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2537; 11601</t>
+          <t>2621; 11839</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2622</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7760</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2796</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1886</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>8226</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>4903</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>2968</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2622</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>7760</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2796</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3425</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4538; 13160</t>
+          <t>661; 6508</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2065; 9176</t>
+          <t>4194; 12799</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>674; 6904</t>
+          <t>749; 6761</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 7385</t>
+          <t>0; 6101</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>653; 6504</t>
+          <t>4761; 13381</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4589; 12861</t>
+          <t>2104; 9141</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>669; 6238</t>
+          <t>669; 7389</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 5880</t>
+          <t>0; 7868</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6726; 16498</t>
+          <t>6927; 16901</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7955; 18591</t>
+          <t>7903; 18909</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2644; 10659</t>
+          <t>2735; 11036</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>871; 8651</t>
+          <t>889; 9518</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>34127</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>35347</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>20895</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>27358</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>41016</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>33681</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>29692</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>30358</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>34127</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>35347</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>20895</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>27344</t>
+          <t>31469</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>57703</t>
+          <t>58826</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>31656; 51695</t>
+          <t>26009; 44051</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25405; 43549</t>
+          <t>27462; 46240</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21662; 39563</t>
+          <t>14512; 29543</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22388; 40492</t>
+          <t>19568; 38410</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>26202; 44209</t>
+          <t>32147; 50973</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25916; 45834</t>
+          <t>25240; 43575</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14275; 28837</t>
+          <t>21157; 39892</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>19431; 39582</t>
+          <t>22628; 42167</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>63049; 88661</t>
+          <t>62255; 89599</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>56237; 81815</t>
+          <t>57198; 82932</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40003; 63213</t>
+          <t>40484; 63374</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>45443; 72984</t>
+          <t>45826; 71936</t>
         </is>
       </c>
     </row>
